--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno3/anno3_task3_question_quality.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno3/anno3_task3_question_quality.xlsx
@@ -1,35 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90652A0B-748B-4548-80D4-2A321E15488D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0899AE5-902B-43B3-AD35-8F98C7CD847E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="159">
   <si>
     <t>UID</t>
   </si>
@@ -70,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000013-0003</t>
-  </si>
-  <si>
-    <t>I've never really thought about it, but I'm interested in exploring more.</t>
-  </si>
-  <si>
-    <t>Have you looked into any other ballets yet?</t>
-  </si>
-  <si>
-    <t>Have you considered looking up any ballet companies in your area?</t>
-  </si>
-  <si>
-    <t>Would you like some recommendations on where to start?</t>
-  </si>
-  <si>
-    <t>Have you ever seen a modern ballet?</t>
-  </si>
-  <si>
-    <t>Do you have any questions about ballet or the performances you're planning to see?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000182-0003</t>
-  </si>
-  <si>
-    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
-  </si>
-  <si>
-    <t>Have you read any books about the Holocaust?</t>
-  </si>
-  <si>
-    <t>Have you ever visited any historical landmarks or sites?</t>
-  </si>
-  <si>
-    <t>Do you think history education should be more comprehensive?</t>
-  </si>
-  <si>
-    <t>Have you read any books on the Holocaust that you would recommend?</t>
-  </si>
-  <si>
-    <t>Have you read any good books about the Holocaust?</t>
+    <t>SFTANNO-000132-0003</t>
+  </si>
+  <si>
+    <t>I'm considering an adventure trip to Patagonia.</t>
+  </si>
+  <si>
+    <t>Have you researched the logistics of the trip?</t>
+  </si>
+  <si>
+    <t>Have you looked into tour operators for the trip?</t>
+  </si>
+  <si>
+    <t>Have you planned the details of your trip?</t>
+  </si>
+  <si>
+    <t>Have you started planning for the trip?</t>
+  </si>
+  <si>
+    <t>Have you started planning your Patagonia adventure?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000107-0003</t>
+  </si>
+  <si>
+    <t>It's so cloudy out, I don't even want to leave my house.</t>
+  </si>
+  <si>
+    <t>Do you have any favorite movies you like to watch on a rainy day?</t>
+  </si>
+  <si>
+    <t>Do you have any upcoming plans for the weekend?</t>
+  </si>
+  <si>
+    <t>Do you have any fun plans coming up?</t>
+  </si>
+  <si>
+    <t>What's your favorite movie?</t>
+  </si>
+  <si>
+    <t>Have you tried any new restaurants lately?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0003</t>
@@ -175,46 +161,46 @@
     <t>Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000156-0003</t>
-  </si>
-  <si>
-    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
-  </si>
-  <si>
-    <t>What are some Feng Shui principles you follow in your own home?</t>
-  </si>
-  <si>
-    <t>Is there anything I can do to feel more confident about it?</t>
-  </si>
-  <si>
-    <t>Do you have any other suggestions for making Feng Shui more manageable?</t>
-  </si>
-  <si>
-    <t>Is there a way to avoid that?</t>
-  </si>
-  <si>
-    <t>What kind of plants would you recommend for beginners?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000007-0003</t>
-  </si>
-  <si>
-    <t>They actually offered me the job!</t>
-  </si>
-  <si>
-    <t>Have you discussed your compensation package with the employer?</t>
-  </si>
-  <si>
-    <t>Have you thought about negotiating your salary or benefits?</t>
-  </si>
-  <si>
-    <t>What are your thoughts on the job offer?</t>
-  </si>
-  <si>
-    <t>Have you thought about negotiating your salary and benefits?</t>
-  </si>
-  <si>
-    <t>Have you started thinking about when you want to start?</t>
+    <t>SFTANNO-000094-0003</t>
+  </si>
+  <si>
+    <t>Actually, I always opt for middle seats. Fewer distractions around me.</t>
+  </si>
+  <si>
+    <t>Do you have any tips for avoiding jet lag?</t>
+  </si>
+  <si>
+    <t>Do you have any travel hacks or tips you like to use?</t>
+  </si>
+  <si>
+    <t>Have you ever met someone interesting on a flight?</t>
+  </si>
+  <si>
+    <t>What's your favorite travel destination?</t>
+  </si>
+  <si>
+    <t>Do you have any travel hacks or tips?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000103-0003</t>
+  </si>
+  <si>
+    <t>I've been browsing, but I don't want to compromise on quality either.</t>
+  </si>
+  <si>
+    <t>Do you have any favorite VR games or experiences?</t>
+  </si>
+  <si>
+    <t>Have you considered waiting for a sale or promotion on the VR headset you want?</t>
+  </si>
+  <si>
+    <t>Have you considered saving up or waiting for sales?</t>
+  </si>
+  <si>
+    <t>Have you considered waiting for a sale or discount?</t>
+  </si>
+  <si>
+    <t>Have you considered any other alternatives or options?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0003</t>
@@ -238,145 +224,151 @@
     <t>Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000167-0003</t>
-  </si>
-  <si>
-    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
-  </si>
-  <si>
-    <t>What do you think is the most exciting development in AI right now?</t>
-  </si>
-  <si>
-    <t>What do you think will be the first significant change we'll see in our daily lives?</t>
-  </si>
-  <si>
-    <t>What do you think will be the first area to see significant change?</t>
-  </si>
-  <si>
-    <t>What kind of AI implementation do you think will be the most beneficial to society?</t>
-  </si>
-  <si>
-    <t>Do you think there are any potential drawbacks?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000001-0003</t>
-  </si>
-  <si>
-    <t>I finished that book you recommended, and it was amazing!</t>
-  </si>
-  <si>
-    <t>What book was it and what did you enjoy about it?</t>
-  </si>
-  <si>
-    <t>Do you have any other recommendations?</t>
-  </si>
-  <si>
-    <t>What's your next book on your list?</t>
-  </si>
-  <si>
-    <t>Do you have any preferences or genres you're interested in?</t>
-  </si>
-  <si>
-    <t>What was your favorite part of the book?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000004-0003</t>
-  </si>
-  <si>
-    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
-  </si>
-  <si>
-    <t>Maybe we can look up some local eye doctors together.</t>
-  </si>
-  <si>
-    <t>Have you considered taking him to an eye doctor for a checkup?</t>
-  </si>
-  <si>
-    <t>Have you noticed any other symptoms?</t>
-  </si>
-  <si>
-    <t>It's important to take care of our eyesight.</t>
-  </si>
-  <si>
-    <t>Have you made an appointment for him yet?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000000-0003</t>
-  </si>
-  <si>
-    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
-  </si>
-  <si>
-    <t>Have you considered reading any other fantasy books in the meantime?</t>
-  </si>
-  <si>
-    <t>Have you thought about what you want to read next?</t>
-  </si>
-  <si>
-    <t>Have you tried talking to someone about it?</t>
-  </si>
-  <si>
-    <t>Have you thought about rereading the series?</t>
-  </si>
-  <si>
-    <t>What's your favorite scene in the book?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000190-0003</t>
-  </si>
-  <si>
-    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
-  </si>
-  <si>
-    <t>How do you balance your TV watching with other activities?</t>
-  </si>
-  <si>
-    <t>Have you tried setting limits for yourself?</t>
-  </si>
-  <si>
-    <t>Have you tried setting a daily limit for watching?</t>
-  </si>
-  <si>
-    <t>Have you tried any TV shows that are less time-consuming?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000161-0003</t>
-  </si>
-  <si>
-    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
-  </si>
-  <si>
-    <t>Have you considered talking to any coworkers about taking action?</t>
-  </si>
-  <si>
-    <t>Have you considered talking to HR about your concerns?</t>
-  </si>
-  <si>
-    <t>Do you think it's worth talking to HR about the handling of this situation?</t>
-  </si>
-  <si>
-    <t>Have you considered reaching out to any other companies or exploring new job opportunities?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000003-0003</t>
-  </si>
-  <si>
-    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
-  </si>
-  <si>
-    <t>Do you have any recommendations for other lenses that I could try?</t>
-  </si>
-  <si>
-    <t>Have you tried using a lens cleaning kit?</t>
-  </si>
-  <si>
-    <t>Have you considered trying out different lenses to find the one that suits your needs?</t>
-  </si>
-  <si>
-    <t>Maybe you can look into buying a new lens?</t>
-  </si>
-  <si>
-    <t>Have you looked into buying a used lens online?</t>
+    <t>SFTANNO-000064-0003</t>
+  </si>
+  <si>
+    <t>I think we should reach out to local organizations and get involved in promoting change.</t>
+  </si>
+  <si>
+    <t>What local organizations do you know of that are promoting change?</t>
+  </si>
+  <si>
+    <t>What local organizations do you recommend we reach out to?</t>
+  </si>
+  <si>
+    <t>What local organizations do you think we should start with?</t>
+  </si>
+  <si>
+    <t>What organizations do you suggest we reach out to?</t>
+  </si>
+  <si>
+    <t>How do you suggest we use social media to spread awareness?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000145-0003</t>
+  </si>
+  <si>
+    <t>That's a great idea! I hadn't thought about that.</t>
+  </si>
+  <si>
+    <t>Do you have any other ideas for making sustainable changes?</t>
+  </si>
+  <si>
+    <t>What other sustainability changes are you thinking about making?</t>
+  </si>
+  <si>
+    <t>What other changes do you want to make in your daily life?</t>
+  </si>
+  <si>
+    <t>Do you have any other sustainability tips or ideas you'd like to share?</t>
+  </si>
+  <si>
+    <t>Have you considered supporting sustainable fashion brands?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000152-0003</t>
+  </si>
+  <si>
+    <t>I'm worried I won't be able to make anything as beautiful as the examples I've seen.</t>
+  </si>
+  <si>
+    <t>Have you considered taking a class to get some hands-on experience?</t>
+  </si>
+  <si>
+    <t>What kind of project are you thinking about making?</t>
+  </si>
+  <si>
+    <t>Have you thought about starting with a simple design and building from there?</t>
+  </si>
+  <si>
+    <t>Have you thought about taking a class to learn some techniques?</t>
+  </si>
+  <si>
+    <t>What kind of scrapbooking materials do you like to use?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000159-0003</t>
+  </si>
+  <si>
+    <t>We should start by setting some ground rules for respectful discussion.</t>
+  </si>
+  <si>
+    <t>How do we create these rules?</t>
+  </si>
+  <si>
+    <t>How can we ensure we follow these rules?</t>
+  </si>
+  <si>
+    <t>What rules do you suggest?</t>
+  </si>
+  <si>
+    <t>What rules do you suggest we implement?</t>
+  </si>
+  <si>
+    <t>What other steps can we take?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000096-0003</t>
+  </si>
+  <si>
+    <t>I missed the last train, and I'm stuck in the city.</t>
+  </si>
+  <si>
+    <t>Is there anything I can do to help you?</t>
+  </si>
+  <si>
+    <t>I'll help you find one if you need it.</t>
+  </si>
+  <si>
+    <t>Do you need help finding a nearby hotel or shelter?</t>
+  </si>
+  <si>
+    <t>Do you have any friends or contacts in the area?</t>
+  </si>
+  <si>
+    <t>Can I help you find a taxi or other transportation option?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000089-0003</t>
+  </si>
+  <si>
+    <t>They have a really solid defense and excellent ball control.</t>
+  </si>
+  <si>
+    <t>Do you have a favorite soccer player?</t>
+  </si>
+  <si>
+    <t>Do you have any upcoming soccer games you're looking forward to?</t>
+  </si>
+  <si>
+    <t>Do you have any other teams you like to watch?</t>
+  </si>
+  <si>
+    <t>Who do you think is the best player on FC Barcelona?</t>
+  </si>
+  <si>
+    <t>Have you ever been to a live soccer game?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000135-0003</t>
+  </si>
+  <si>
+    <t>I did a river rafting trip once, but the water was so dirty.</t>
+  </si>
+  <si>
+    <t>Have you tried any other outdoor adventures?</t>
+  </si>
+  <si>
+    <t>Have you ever tried whitewater rafting in a clean river?</t>
+  </si>
+  <si>
+    <t>Have you ever tried any adventure sports that involve water?</t>
+  </si>
+  <si>
+    <t>Have you gone rafting on a cleaner river since then?</t>
+  </si>
+  <si>
+    <t>Have you ever gone on a clean and safe river rafting trip?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0003</t>
@@ -397,46 +389,46 @@
     <t>Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000002-0003</t>
-  </si>
-  <si>
-    <t>Not yet, everything is still uncertain due to the pandemic.</t>
-  </si>
-  <si>
-    <t>How do you stay motivated during these tough times?</t>
-  </si>
-  <si>
-    <t>Do you have any other projects in mind?</t>
-  </si>
-  <si>
-    <t>Have you considered virtual events or book clubs?</t>
-  </si>
-  <si>
-    <t>When do you plan to release your book?</t>
-  </si>
-  <si>
-    <t>Have you considered virtual events or book readings?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000172-0003</t>
-  </si>
-  <si>
-    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
-  </si>
-  <si>
-    <t>How do you cope with their disbelief?</t>
-  </si>
-  <si>
-    <t>Do you think there's a way to change their perspective?</t>
-  </si>
-  <si>
-    <t>Would you like me to help you write a post about mindfulness?</t>
-  </si>
-  <si>
-    <t>Have you found other mindfulness enthusiasts to share your experiences with?</t>
-  </si>
-  <si>
-    <t>Have you considered finding like-minded individuals to discuss mindfulness with?</t>
+    <t>SFTANNO-000163-0003</t>
+  </si>
+  <si>
+    <t>I wish I could go back in time to see history up close.</t>
+  </si>
+  <si>
+    <t>What historical event would you like to witness if you could?</t>
+  </si>
+  <si>
+    <t>Have you ever visited any historical sites?</t>
+  </si>
+  <si>
+    <t>Have you ever read a book about a historical event?</t>
+  </si>
+  <si>
+    <t>It's important to appreciate history as it is, not just wish we could change it.</t>
+  </si>
+  <si>
+    <t>It's always important to appreciate and learn from the past.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000102-0003</t>
+  </si>
+  <si>
+    <t>The new Pokemon game is such a cash grab. They're releasing the same version with only minor updates.</t>
+  </si>
+  <si>
+    <t>Have you tried playing any other Pokemon games in the meantime?</t>
+  </si>
+  <si>
+    <t>Have you tried playing any of the older Pokemon games?</t>
+  </si>
+  <si>
+    <t>What other games have you been playing lately?</t>
+  </si>
+  <si>
+    <t>Have you considered trying a different game instead?</t>
+  </si>
+  <si>
+    <t>What other Pokemon games have you played?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0003</t>
@@ -481,31 +473,25 @@
     <t>Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000176-0003</t>
-  </si>
-  <si>
-    <t>No, just a pot for the pasta and a pan for the sauce.</t>
-  </si>
-  <si>
-    <t>When should I start?</t>
-  </si>
-  <si>
-    <t>Have you tried any other easy recipes lately?</t>
-  </si>
-  <si>
-    <t>How long do you think it'll take to make?</t>
-  </si>
-  <si>
-    <t>Thanks for sharing this recipe with me.</t>
-  </si>
-  <si>
-    <t>Let me know if you need any more tips or help.</t>
-  </si>
-  <si>
-    <t>Falta contexto</t>
-  </si>
-  <si>
-    <t>Las preguntas no tienen mucho sentido ya que la persona no sabe del tema</t>
+    <t>SFTANNO-000062-0003</t>
+  </si>
+  <si>
+    <t>I'm thrilled to see more young people engaging in politics.</t>
+  </si>
+  <si>
+    <t>Have you engaged with any youth activism groups?</t>
+  </si>
+  <si>
+    <t>Have you considered organizing events or workshops to encourage political participation?</t>
+  </si>
+  <si>
+    <t>Have you been following any inspiring young politicians or activists?</t>
+  </si>
+  <si>
+    <t>How do you think we can continue encouraging young people to stay engaged?</t>
+  </si>
+  <si>
+    <t>Have you considered mentoring or supporting young political activists?</t>
   </si>
 </sst>
 </file>
@@ -524,6 +510,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -874,22 +861,12 @@
   <dimension ref="A1:M22"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.88671875" style="2" customWidth="1"/>
-    <col min="2" max="3" width="27.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="27.5546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="7" width="27.5546875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="8.21875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="27.5546875" style="2" customWidth="1"/>
-    <col min="10" max="10" width="8" style="2" customWidth="1"/>
-    <col min="11" max="11" width="27.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" style="2" customWidth="1"/>
-    <col min="13" max="13" width="4.109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.6640625" style="2" customWidth="1"/>
+    <col min="2" max="13" width="27.33203125" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -930,7 +907,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -941,31 +918,31 @@
         <v>15</v>
       </c>
       <c r="D2" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H2" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>18</v>
       </c>
       <c r="J2" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -979,13 +956,13 @@
         <v>22</v>
       </c>
       <c r="D3" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="F3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
@@ -1003,10 +980,10 @@
         <v>26</v>
       </c>
       <c r="L3" s="2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1017,7 +994,7 @@
         <v>29</v>
       </c>
       <c r="D4" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
@@ -1029,7 +1006,7 @@
         <v>31</v>
       </c>
       <c r="H4" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
@@ -1044,7 +1021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1067,19 +1044,19 @@
         <v>38</v>
       </c>
       <c r="H5" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
       <c r="J5" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
       <c r="L5" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
@@ -1093,34 +1070,34 @@
         <v>43</v>
       </c>
       <c r="D6" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
       <c r="F6" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
       <c r="H6" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
       <c r="J6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
       <c r="L6" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1131,19 +1108,19 @@
         <v>50</v>
       </c>
       <c r="D7" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H7" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
@@ -1175,25 +1152,25 @@
         <v>58</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
       <c r="H8" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
       </c>
       <c r="J8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
       <c r="L8" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1207,19 +1184,19 @@
         <v>64</v>
       </c>
       <c r="D9" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
       <c r="H9" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
@@ -1231,7 +1208,7 @@
         <v>68</v>
       </c>
       <c r="L9" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1245,25 +1222,25 @@
         <v>71</v>
       </c>
       <c r="D10" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F10" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
       <c r="H10" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
       <c r="J10" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
@@ -1295,19 +1272,19 @@
         <v>80</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
       <c r="J11" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="L11" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1321,13 +1298,13 @@
         <v>85</v>
       </c>
       <c r="D12" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>86</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
@@ -1339,7 +1316,7 @@
         <v>88</v>
       </c>
       <c r="J12" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
@@ -1359,31 +1336,31 @@
         <v>92</v>
       </c>
       <c r="D13" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H13" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
       <c r="J13" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
       <c r="L13" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
@@ -1397,7 +1374,7 @@
         <v>99</v>
       </c>
       <c r="D14" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
@@ -1406,343 +1383,331 @@
         <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H14" s="2">
         <v>5</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J14" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L14" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="57.6" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D15" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F15" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H15" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J15" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="L15" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D16" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F16" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H16" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J16" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="L16" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D17" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F17" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="2">
+        <v>4</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="H17" s="2">
-        <v>3</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>118</v>
-      </c>
       <c r="J17" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="L17" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="72" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D18" s="2">
         <v>1</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H18" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J18" s="2">
         <v>5</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="L18" s="2">
-        <v>4</v>
-      </c>
-      <c r="M18" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D19" s="2">
+        <v>2</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19" s="2">
+        <v>5</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="2">
+        <v>4</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J19" s="2">
+        <v>3</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="2">
+        <v>1</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="2">
+        <v>3</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="2">
+        <v>5</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="2">
+        <v>5</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="2">
+        <v>4</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="J21" s="2">
+        <v>3</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L21" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D22" s="2">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="F22" s="2">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="2">
+        <v>4</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="2">
-        <v>2</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F19" s="2">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H19" s="2">
-        <v>3</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="2">
-        <v>4</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L19" s="2">
-        <v>5</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D20" s="2">
-        <v>4</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F20" s="2">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="H20" s="2">
-        <v>1</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="J20" s="2">
-        <v>3</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="L20" s="2">
-        <v>5</v>
-      </c>
-      <c r="M20" s="2" t="s">
+      <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="D21" s="2">
-        <v>4</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F21" s="2">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="H21" s="2">
-        <v>3</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L21" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="72" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="2">
-        <v>1</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="F22" s="2">
-        <v>2</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="H22" s="2">
-        <v>4</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="J22" s="2">
-        <v>3</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="L22" s="2">
         <v>5</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>157</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{72B59FD3-0C5A-4CC4-B782-D55A8BEC064B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{CF72A3CD-43BC-4566-84F7-204132638037}">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>
